--- a/conf/xdr_check_template-ctcc.xlsx
+++ b/conf/xdr_check_template-ctcc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BaiduSyncdisk\my_code\repo\gotools\go_xdrCheck\conf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A6568C-F136-42C6-B94A-BBA0FF72E960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD50FF6-AF82-4DF0-830F-433FF6B1CDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="文件校验" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="804">
   <si>
     <t>sheet名称</t>
   </si>
@@ -14885,12 +14885,41 @@
     <t>DEFAULT.manufacture_id</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
+  <si>
+    <t>len&lt;2049</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选填</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>|if($5==1)</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>len&lt;129</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -14979,6 +15008,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -15055,7 +15091,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -15265,6 +15301,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -25857,11 +25896,11 @@
       <c r="D8" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>724</v>
+      <c r="E8" s="70" t="s">
+        <v>802</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>71</v>
+        <v>803</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>725</v>
@@ -25885,7 +25924,7 @@
         <v>724</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>103</v>
+        <v>801</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>726</v>

--- a/conf/xdr_check_template-ctcc.xlsx
+++ b/conf/xdr_check_template-ctcc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BaiduSyncdisk\my_code\repo\gotools\go_xdrCheck\conf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD50FF6-AF82-4DF0-830F-433FF6B1CDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A6568C-F136-42C6-B94A-BBA0FF72E960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="文件校验" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="801">
   <si>
     <t>sheet名称</t>
   </si>
@@ -14885,41 +14885,12 @@
     <t>DEFAULT.manufacture_id</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
-  <si>
-    <t>len&lt;2049</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>选填</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>|if($5==1)</t>
-    </r>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>len&lt;129</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -15008,13 +14979,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -15091,7 +15055,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -15301,9 +15265,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -25896,11 +25857,11 @@
       <c r="D8" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="70" t="s">
-        <v>802</v>
+      <c r="E8" s="2" t="s">
+        <v>724</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>803</v>
+        <v>71</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>725</v>
@@ -25924,7 +25885,7 @@
         <v>724</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>801</v>
+        <v>103</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>726</v>
